--- a/artfynd/A 43381-2026 artfynd.xlsx
+++ b/artfynd/A 43381-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137441605</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137441606</v>
       </c>
       <c r="B3" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137441603</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43381-2026 artfynd.xlsx
+++ b/artfynd/A 43381-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,1030 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137441603</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137433553</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>741104</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7305262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433553</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137433557</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>741044</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7305220</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433557</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137433560</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>741077</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7305153</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433560</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137433561</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>741123</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7305070</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433561</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137433552</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79559</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>741129</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7305230</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433552</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137433558</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80650</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>741063</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7305169</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433558</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137433559</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80655</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>741065</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7305168</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137433551</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>741133</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7305228</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433551</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137433562</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98296</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>741124</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7305083</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433562</t>
         </is>
       </c>
     </row>
@@ -1019,6 +2043,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43381-2026 artfynd.xlsx
+++ b/artfynd/A 43381-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137441605</v>
       </c>
       <c r="B2" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137441606</v>
       </c>
       <c r="B3" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137441603</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137433553</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137433557</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137433560</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137433561</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137433552</v>
       </c>
       <c r="B9" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137433558</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137433559</v>
       </c>
       <c r="B11" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>137433551</v>
       </c>
       <c r="B12" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>137433562</v>
       </c>
       <c r="B13" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
